--- a/salidas/empresas/LRCX.xlsx
+++ b/salidas/empresas/LRCX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>3.934914350509644</v>
+        <v>3.93491530418396</v>
       </c>
       <c r="C2" t="n">
         <v>4.64300012588501</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>3.652700424194336</v>
+        <v>3.652698755264282</v>
       </c>
       <c r="C3" t="n">
         <v>4.309999942779541</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>3.644225358963013</v>
+        <v>3.644224643707275</v>
       </c>
       <c r="C4" t="n">
         <v>4.300000190734863</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>4.142551422119141</v>
+        <v>4.142552375793457</v>
       </c>
       <c r="C5" t="n">
         <v>4.888000011444092</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>3.795927047729492</v>
+        <v>3.795926570892334</v>
       </c>
       <c r="C6" t="n">
         <v>4.479000091552734</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>3.959493160247803</v>
+        <v>3.959491968154907</v>
       </c>
       <c r="C7" t="n">
         <v>4.671999931335449</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>3.525576829910278</v>
+        <v>3.525575876235962</v>
       </c>
       <c r="C8" t="n">
         <v>4.159999847412109</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>3.621342420578003</v>
+        <v>3.621342658996582</v>
       </c>
       <c r="C9" t="n">
         <v>4.27299976348877</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>3.841690301895142</v>
+        <v>3.841691970825195</v>
       </c>
       <c r="C10" t="n">
         <v>4.532999992370605</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>4.190858840942383</v>
+        <v>4.190860271453857</v>
       </c>
       <c r="C11" t="n">
         <v>4.945000171661377</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>4.457819938659668</v>
+        <v>4.457820892333984</v>
       </c>
       <c r="C12" t="n">
         <v>5.260000228881836</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>4.290015697479248</v>
+        <v>4.290016651153564</v>
       </c>
       <c r="C13" t="n">
         <v>5.061999797821045</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>3.882369995117188</v>
+        <v>3.882370710372925</v>
       </c>
       <c r="C14" t="n">
         <v>4.580999851226807</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>3.784907817840576</v>
+        <v>3.784908294677734</v>
       </c>
       <c r="C15" t="n">
         <v>4.466000080108643</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>4.012038707733154</v>
+        <v>4.01203727722168</v>
       </c>
       <c r="C16" t="n">
         <v>4.734000205993652</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>4.557823181152344</v>
+        <v>4.55782413482666</v>
       </c>
       <c r="C17" t="n">
         <v>5.377999782562256</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>4.55273962020874</v>
+        <v>4.552739143371582</v>
       </c>
       <c r="C18" t="n">
         <v>5.372000217437744</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>4.356120109558105</v>
+        <v>4.356118679046631</v>
       </c>
       <c r="C19" t="n">
         <v>5.139999866485596</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>4.90190601348877</v>
+        <v>4.901907444000244</v>
       </c>
       <c r="C20" t="n">
         <v>5.783999919891357</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>4.513754367828369</v>
+        <v>4.513755321502686</v>
       </c>
       <c r="C22" t="n">
         <v>5.326000213623047</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>3.885760307312012</v>
+        <v>3.885761022567749</v>
       </c>
       <c r="C24" t="n">
         <v>4.585000038146973</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>3.663716793060303</v>
+        <v>3.663717985153198</v>
       </c>
       <c r="C25" t="n">
         <v>4.322999954223633</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>3.253530502319336</v>
+        <v>3.253530025482178</v>
       </c>
       <c r="C26" t="n">
         <v>3.83899998664856</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>3.239122152328491</v>
+        <v>3.239123106002808</v>
       </c>
       <c r="C28" t="n">
         <v>3.822000026702881</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>3.461166381835938</v>
+        <v>3.461166620254517</v>
       </c>
       <c r="C29" t="n">
         <v>4.084000110626221</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>3.449301242828369</v>
+        <v>3.449301719665527</v>
       </c>
       <c r="C30" t="n">
         <v>4.070000171661377</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>3.06369161605835</v>
+        <v>3.063691139221191</v>
       </c>
       <c r="C31" t="n">
         <v>3.615000009536743</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>2.787408590316772</v>
+        <v>2.787408113479614</v>
       </c>
       <c r="C32" t="n">
         <v>3.289000034332275</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>3.115388631820679</v>
+        <v>3.115389108657837</v>
       </c>
       <c r="C33" t="n">
         <v>3.676000118255615</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>2.668758392333984</v>
+        <v>2.668759346008301</v>
       </c>
       <c r="C34" t="n">
         <v>3.148999929428101</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>1.894997477531433</v>
+        <v>1.894997239112854</v>
       </c>
       <c r="C35" t="n">
         <v>2.236000061035156</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>1.711938142776489</v>
+        <v>1.7119380235672</v>
       </c>
       <c r="C36" t="n">
         <v>2.019999980926514</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>1.803467750549316</v>
+        <v>1.803467988967896</v>
       </c>
       <c r="C37" t="n">
         <v>2.128000020980835</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>1.712785840034485</v>
+        <v>1.712786078453064</v>
       </c>
       <c r="C38" t="n">
         <v>2.020999908447266</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>1.657698512077332</v>
+        <v>1.657698631286621</v>
       </c>
       <c r="C39" t="n">
         <v>1.955999970436096</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>1.929744601249695</v>
+        <v>1.929744482040405</v>
       </c>
       <c r="C40" t="n">
         <v>2.276999950408936</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>2.362812995910645</v>
+        <v>2.36281418800354</v>
       </c>
       <c r="C41" t="n">
         <v>2.788000106811523</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>2.219587802886963</v>
+        <v>2.219587564468384</v>
       </c>
       <c r="C42" t="n">
         <v>2.61899995803833</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>2.547568559646606</v>
+        <v>2.547567844390869</v>
       </c>
       <c r="C44" t="n">
         <v>3.00600004196167</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>2.601807594299316</v>
+        <v>2.601807117462158</v>
       </c>
       <c r="C45" t="n">
         <v>3.069999933242798</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>2.895039319992065</v>
+        <v>2.895039558410645</v>
       </c>
       <c r="C46" t="n">
         <v>3.415999889373779</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>2.857749938964844</v>
+        <v>2.857750415802002</v>
       </c>
       <c r="C47" t="n">
         <v>3.371999979019165</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>2.880633592605591</v>
+        <v>2.880631685256958</v>
       </c>
       <c r="C48" t="n">
         <v>3.398999929428101</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>3.323024034500122</v>
+        <v>3.323024749755859</v>
       </c>
       <c r="C49" t="n">
         <v>3.921000003814697</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>2.797579050064087</v>
+        <v>2.79757833480835</v>
       </c>
       <c r="C50" t="n">
         <v>3.301000118255615</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>2.873852729797363</v>
+        <v>2.873852491378784</v>
       </c>
       <c r="C51" t="n">
         <v>3.391000032424927</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>3.162847280502319</v>
+        <v>3.162847995758057</v>
       </c>
       <c r="C52" t="n">
         <v>3.732000112533569</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>3.435742139816284</v>
+        <v>3.435741662979126</v>
       </c>
       <c r="C53" t="n">
         <v>4.053999900817871</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>3.208613395690918</v>
+        <v>3.20861291885376</v>
       </c>
       <c r="C54" t="n">
         <v>3.78600001335144</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>3.225562810897827</v>
+        <v>3.225563526153564</v>
       </c>
       <c r="C55" t="n">
         <v>3.805999994277954</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>3.575577735900879</v>
+        <v>3.575577259063721</v>
       </c>
       <c r="C56" t="n">
         <v>4.218999862670898</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>3.060301780700684</v>
+        <v>3.060300827026367</v>
       </c>
       <c r="C57" t="n">
         <v>3.611000061035156</v>
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>3.546764135360718</v>
+        <v>3.546763181686401</v>
       </c>
       <c r="C58" t="n">
         <v>4.184999942779541</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>3.880675554275513</v>
+        <v>3.880675315856934</v>
       </c>
       <c r="C59" t="n">
         <v>4.578999996185303</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>3.847621917724609</v>
+        <v>3.847624778747559</v>
       </c>
       <c r="C60" t="n">
         <v>4.539999961853027</v>
@@ -1609,11 +1621,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>4.388325214385986</v>
+        <v>4.38832426071167</v>
       </c>
       <c r="C61" t="n">
         <v>5.177999973297119</v>
@@ -1634,11 +1646,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>4.228148937225342</v>
+        <v>4.2281494140625</v>
       </c>
       <c r="C62" t="n">
         <v>4.988999843597412</v>
@@ -1659,7 +1671,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1684,11 +1696,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>4.801902294158936</v>
+        <v>4.801901817321777</v>
       </c>
       <c r="C64" t="n">
         <v>5.665999889373779</v>
@@ -1709,11 +1721,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>4.094244003295898</v>
+        <v>4.094244480133057</v>
       </c>
       <c r="C65" t="n">
         <v>4.830999851226807</v>
@@ -1734,11 +1746,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>3.982374668121338</v>
+        <v>3.982376098632812</v>
       </c>
       <c r="C66" t="n">
         <v>4.698999881744385</v>
@@ -1759,11 +1771,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>3.752705335617065</v>
+        <v>3.752703905105591</v>
       </c>
       <c r="C67" t="n">
         <v>4.427999973297119</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>3.464556694030762</v>
+        <v>3.464556455612183</v>
       </c>
       <c r="C68" t="n">
         <v>4.087999820709229</v>
@@ -1809,11 +1821,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>3.149288654327393</v>
+        <v>3.149288177490234</v>
       </c>
       <c r="C69" t="n">
         <v>3.716000080108643</v>
@@ -1838,11 +1850,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>3.218783378601074</v>
+        <v>3.218782424926758</v>
       </c>
       <c r="C70" t="n">
         <v>3.79800009727478</v>
@@ -1867,11 +1879,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>3.643378019332886</v>
+        <v>3.643377065658569</v>
       </c>
       <c r="C71" t="n">
         <v>4.298999786376953</v>
@@ -1896,11 +1908,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>3.455234527587891</v>
+        <v>3.455233335494995</v>
       </c>
       <c r="C72" t="n">
         <v>4.077000141143799</v>
@@ -1925,11 +1937,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>3.137423276901245</v>
+        <v>3.137422800064087</v>
       </c>
       <c r="C73" t="n">
         <v>3.70199990272522</v>
@@ -1954,11 +1966,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>3.609477758407593</v>
+        <v>3.609476804733276</v>
       </c>
       <c r="C74" t="n">
         <v>4.258999824523926</v>
@@ -1983,7 +1995,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2012,11 +2024,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>3.781518936157227</v>
+        <v>3.781519174575806</v>
       </c>
       <c r="C76" t="n">
         <v>4.461999893188477</v>
@@ -2041,11 +2053,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>3.531508445739746</v>
+        <v>3.531508684158325</v>
       </c>
       <c r="C77" t="n">
         <v>4.166999816894531</v>
@@ -2070,11 +2082,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>3.161152839660645</v>
+        <v>3.161153078079224</v>
       </c>
       <c r="C78" t="n">
         <v>3.730000019073486</v>
@@ -2099,11 +2111,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>3.198443174362183</v>
+        <v>3.198442220687866</v>
       </c>
       <c r="C79" t="n">
         <v>3.773999929428101</v>
@@ -2128,11 +2140,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>2.9162278175354</v>
+        <v>2.916226863861084</v>
       </c>
       <c r="C80" t="n">
         <v>3.440999984741211</v>
@@ -2157,11 +2169,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>2.892498016357422</v>
+        <v>2.892497777938843</v>
       </c>
       <c r="C81" t="n">
         <v>3.413000106811523</v>
@@ -2186,7 +2198,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2215,7 +2227,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2244,7 +2256,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2273,11 +2285,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>3.061996936798096</v>
+        <v>3.061996459960938</v>
       </c>
       <c r="C85" t="n">
         <v>3.61299991607666</v>
@@ -2302,11 +2314,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>3.486591577529907</v>
+        <v>3.486591100692749</v>
       </c>
       <c r="C86" t="n">
         <v>4.113999843597412</v>
@@ -2331,11 +2343,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>3.584899425506592</v>
+        <v>3.584899663925171</v>
       </c>
       <c r="C87" t="n">
         <v>4.230000019073486</v>
@@ -2360,11 +2372,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>3.513710975646973</v>
+        <v>3.513710260391235</v>
       </c>
       <c r="C88" t="n">
         <v>4.145999908447266</v>
@@ -2389,7 +2401,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2418,11 +2430,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>3.964576482772827</v>
+        <v>3.96457839012146</v>
       </c>
       <c r="C90" t="n">
         <v>4.677999973297119</v>
@@ -2447,11 +2459,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>3.757787942886353</v>
+        <v>3.757791042327881</v>
       </c>
       <c r="C91" t="n">
         <v>4.434000015258789</v>
@@ -2476,11 +2488,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>4.171366214752197</v>
+        <v>4.171365737915039</v>
       </c>
       <c r="C92" t="n">
         <v>4.921999931335449</v>
@@ -2505,7 +2517,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2534,11 +2546,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>4.339169979095459</v>
+        <v>4.339169025421143</v>
       </c>
       <c r="C94" t="n">
         <v>5.119999885559082</v>
@@ -2563,11 +2575,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>4.599349975585938</v>
+        <v>4.599350452423096</v>
       </c>
       <c r="C95" t="n">
         <v>5.427000045776367</v>
@@ -2592,11 +2604,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>4.416292190551758</v>
+        <v>4.416291236877441</v>
       </c>
       <c r="C96" t="n">
         <v>5.210999965667725</v>
@@ -2621,11 +2633,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>4.614607334136963</v>
+        <v>4.614606380462646</v>
       </c>
       <c r="C97" t="n">
         <v>5.445000171661377</v>
@@ -2650,11 +2662,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>4.289168357849121</v>
+        <v>4.289167881011963</v>
       </c>
       <c r="C98" t="n">
         <v>5.060999870300293</v>
@@ -2679,11 +2691,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>4.384087085723877</v>
+        <v>4.384088039398193</v>
       </c>
       <c r="C99" t="n">
         <v>5.172999858856201</v>
@@ -2708,11 +2720,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>4.661218643188477</v>
+        <v>4.661218166351318</v>
       </c>
       <c r="C100" t="n">
         <v>5.5</v>
@@ -2737,11 +2749,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>4.882412910461426</v>
+        <v>4.8824143409729</v>
       </c>
       <c r="C101" t="n">
         <v>5.761000156402588</v>
@@ -2766,11 +2778,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>5.257855415344238</v>
+        <v>5.25785493850708</v>
       </c>
       <c r="C102" t="n">
         <v>6.203999996185303</v>
@@ -2795,11 +2807,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>5.743270874023438</v>
+        <v>5.743270397186279</v>
       </c>
       <c r="C103" t="n">
         <v>6.757999897003174</v>
@@ -2824,11 +2836,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>5.948932647705078</v>
+        <v>5.948934555053711</v>
       </c>
       <c r="C104" t="n">
         <v>7</v>
@@ -2853,11 +2865,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>6.111254215240479</v>
+        <v>6.111253261566162</v>
       </c>
       <c r="C105" t="n">
         <v>7.190999984741211</v>
@@ -2882,11 +2894,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>6.364279270172119</v>
+        <v>6.364280223846436</v>
       </c>
       <c r="C106" t="n">
         <v>7.46999979019165</v>
@@ -2911,7 +2923,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -2940,7 +2952,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -2969,11 +2981,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>6.774060249328613</v>
+        <v>6.774062633514404</v>
       </c>
       <c r="C109" t="n">
         <v>7.934000015258789</v>
@@ -2998,11 +3010,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>6.526456832885742</v>
+        <v>6.526459217071533</v>
       </c>
       <c r="C110" t="n">
         <v>7.644000053405762</v>
@@ -3027,11 +3039,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>7.040447235107422</v>
+        <v>7.04044771194458</v>
       </c>
       <c r="C111" t="n">
         <v>8.246000289916992</v>
@@ -3056,7 +3068,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3085,11 +3097,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>6.467554569244385</v>
+        <v>6.467552185058594</v>
       </c>
       <c r="C113" t="n">
         <v>7.558000087738037</v>
@@ -3114,11 +3126,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>7.038321971893311</v>
+        <v>7.038321018218994</v>
       </c>
       <c r="C114" t="n">
         <v>8.225000381469727</v>
@@ -3143,11 +3155,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>6.986425399780273</v>
+        <v>6.986424922943115</v>
       </c>
       <c r="C115" t="n">
         <v>8.135000228881836</v>
@@ -3172,11 +3184,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>6.601677417755127</v>
+        <v>6.601677894592285</v>
       </c>
       <c r="C116" t="n">
         <v>7.686999797821045</v>
@@ -3201,11 +3213,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>6.249566078186035</v>
+        <v>6.249565124511719</v>
       </c>
       <c r="C117" t="n">
         <v>7.276999950408936</v>
@@ -3230,11 +3242,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>5.634168148040771</v>
+        <v>5.63416576385498</v>
       </c>
       <c r="C118" t="n">
         <v>6.532999992370605</v>
@@ -3259,11 +3271,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>6.605250835418701</v>
+        <v>6.605248928070068</v>
       </c>
       <c r="C119" t="n">
         <v>7.658999919891357</v>
@@ -3288,7 +3300,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3317,11 +3329,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>6.875865459442139</v>
+        <v>6.875867366790771</v>
       </c>
       <c r="C121" t="n">
         <v>7.941999912261963</v>
@@ -3346,11 +3358,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>6.215291976928711</v>
+        <v>6.215291023254395</v>
       </c>
       <c r="C122" t="n">
         <v>7.178999900817871</v>
@@ -3375,11 +3387,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>6.346020698547363</v>
+        <v>6.346021175384521</v>
       </c>
       <c r="C123" t="n">
         <v>7.329999923706055</v>
@@ -3404,11 +3416,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>7.180158615112305</v>
+        <v>7.180158138275146</v>
       </c>
       <c r="C124" t="n">
         <v>8.260000228881836</v>
@@ -3433,11 +3445,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>6.64121150970459</v>
+        <v>6.641211986541748</v>
       </c>
       <c r="C125" t="n">
         <v>7.639999866485596</v>
@@ -3462,7 +3474,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3491,11 +3503,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>7.333548545837402</v>
+        <v>7.333547115325928</v>
       </c>
       <c r="C127" t="n">
         <v>8.406000137329102</v>
@@ -3520,11 +3532,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>7.831695079803467</v>
+        <v>7.831699848175049</v>
       </c>
       <c r="C128" t="n">
         <v>8.97700023651123</v>
@@ -3549,11 +3561,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>8.14140510559082</v>
+        <v>8.141407012939453</v>
       </c>
       <c r="C129" t="n">
         <v>9.331999778747559</v>
@@ -3578,11 +3590,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>8.289943695068359</v>
+        <v>8.289946556091309</v>
       </c>
       <c r="C130" t="n">
         <v>9.470999717712402</v>
@@ -3607,11 +3619,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>8.478137016296387</v>
+        <v>8.478137969970703</v>
       </c>
       <c r="C131" t="n">
         <v>9.685999870300293</v>
@@ -3636,7 +3648,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3665,11 +3677,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>9.294709205627441</v>
+        <v>9.294712066650391</v>
       </c>
       <c r="C133" t="n">
         <v>10.57299995422363</v>
@@ -3694,11 +3706,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>10.09732818603516</v>
+        <v>10.09732532501221</v>
       </c>
       <c r="C134" t="n">
         <v>11.48600006103516</v>
@@ -3723,7 +3735,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3752,11 +3764,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>11.3270788192749</v>
+        <v>11.32707977294922</v>
       </c>
       <c r="C136" t="n">
         <v>12.83600044250488</v>
@@ -3781,11 +3793,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>12.78223323822021</v>
+        <v>12.78223037719727</v>
       </c>
       <c r="C137" t="n">
         <v>14.48499965667725</v>
@@ -3810,11 +3822,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>13.69291877746582</v>
+        <v>13.69291210174561</v>
       </c>
       <c r="C138" t="n">
         <v>15.51700019836426</v>
@@ -3839,7 +3851,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3868,7 +3880,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3897,11 +3909,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>14.68847751617432</v>
+        <v>14.68847560882568</v>
       </c>
       <c r="C141" t="n">
         <v>16.59799957275391</v>
@@ -3926,7 +3938,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3955,11 +3967,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>18.50650405883789</v>
+        <v>18.50650215148926</v>
       </c>
       <c r="C143" t="n">
         <v>20.85700035095215</v>
@@ -3984,11 +3996,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>17.06552505493164</v>
+        <v>17.06552314758301</v>
       </c>
       <c r="C144" t="n">
         <v>19.23299980163574</v>
@@ -4013,7 +4025,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4042,11 +4054,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>17.04078674316406</v>
+        <v>17.04079246520996</v>
       </c>
       <c r="C146" t="n">
         <v>19.15200042724609</v>
@@ -4071,11 +4083,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>17.07104301452637</v>
+        <v>17.07104682922363</v>
       </c>
       <c r="C147" t="n">
         <v>19.18600082397461</v>
@@ -4100,11 +4112,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>18.12207794189453</v>
+        <v>18.1220817565918</v>
       </c>
       <c r="C148" t="n">
         <v>20.31599998474121</v>
@@ -4129,11 +4141,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>16.50753974914551</v>
+        <v>16.50754547119141</v>
       </c>
       <c r="C149" t="n">
         <v>18.50600051879883</v>
@@ -4158,11 +4170,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>17.67786026000977</v>
+        <v>17.67786598205566</v>
       </c>
       <c r="C150" t="n">
         <v>19.81800079345703</v>
@@ -4187,11 +4199,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>15.50173854827881</v>
+        <v>15.50174331665039</v>
       </c>
       <c r="C151" t="n">
         <v>17.28499984741211</v>
@@ -4216,7 +4228,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4245,11 +4257,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>15.52326679229736</v>
+        <v>15.52326488494873</v>
       </c>
       <c r="C153" t="n">
         <v>17.30900001525879</v>
@@ -4274,7 +4286,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4303,11 +4315,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>12.79909324645996</v>
+        <v>12.79909420013428</v>
       </c>
       <c r="C155" t="n">
         <v>14.17300033569336</v>
@@ -4332,11 +4344,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>14.1744556427002</v>
+        <v>14.17445850372314</v>
       </c>
       <c r="C156" t="n">
         <v>15.69600009918213</v>
@@ -4361,11 +4373,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>12.3815746307373</v>
+        <v>12.38157367706299</v>
       </c>
       <c r="C157" t="n">
         <v>13.61699962615967</v>
@@ -4390,11 +4402,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>15.41945838928223</v>
+        <v>15.41945552825928</v>
       </c>
       <c r="C158" t="n">
         <v>16.95800018310547</v>
@@ -4419,11 +4431,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>16.01139450073242</v>
+        <v>16.01140022277832</v>
       </c>
       <c r="C159" t="n">
         <v>17.60899925231934</v>
@@ -4448,11 +4460,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>16.37687110900879</v>
+        <v>16.37687301635742</v>
       </c>
       <c r="C160" t="n">
         <v>17.90099906921387</v>
@@ -4477,11 +4489,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>18.97689437866211</v>
+        <v>18.97690200805664</v>
       </c>
       <c r="C161" t="n">
         <v>20.74300003051758</v>
@@ -4506,11 +4518,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>15.97433376312256</v>
+        <v>15.97433948516846</v>
       </c>
       <c r="C162" t="n">
         <v>17.46100044250488</v>
@@ -4535,7 +4547,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4564,11 +4576,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>19.19530487060547</v>
+        <v>19.1953010559082</v>
       </c>
       <c r="C164" t="n">
         <v>20.86100006103516</v>
@@ -4593,7 +4605,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4622,11 +4634,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>21.37246894836426</v>
+        <v>21.37247085571289</v>
       </c>
       <c r="C166" t="n">
         <v>23.11100006103516</v>
@@ -4651,11 +4663,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>25.06509971618652</v>
+        <v>25.06509780883789</v>
       </c>
       <c r="C167" t="n">
         <v>27.10400009155273</v>
@@ -4680,11 +4692,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>24.67576599121094</v>
+        <v>24.67576789855957</v>
       </c>
       <c r="C168" t="n">
         <v>26.6830005645752</v>
@@ -4709,11 +4721,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>27.15693855285645</v>
+        <v>27.15693664550781</v>
       </c>
       <c r="C169" t="n">
         <v>29.23999977111816</v>
@@ -4738,11 +4750,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>27.6965446472168</v>
+        <v>27.69654655456543</v>
       </c>
       <c r="C170" t="n">
         <v>29.82099914550781</v>
@@ -4767,11 +4779,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>27.25260543823242</v>
+        <v>27.25259971618652</v>
       </c>
       <c r="C171" t="n">
         <v>29.3430004119873</v>
@@ -4796,11 +4808,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>22.42395210266113</v>
+        <v>22.42395401000977</v>
       </c>
       <c r="C172" t="n">
         <v>24</v>
@@ -4825,11 +4837,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>23.85161209106445</v>
+        <v>23.85161399841309</v>
       </c>
       <c r="C173" t="n">
         <v>25.52799987792969</v>
@@ -4854,11 +4866,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>25.56984710693359</v>
+        <v>25.56985473632812</v>
       </c>
       <c r="C174" t="n">
         <v>27.36700057983398</v>
@@ -4883,7 +4895,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4912,11 +4924,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>35.37899017333984</v>
+        <v>35.37899780273438</v>
       </c>
       <c r="C176" t="n">
         <v>37.71599960327148</v>
@@ -4941,11 +4953,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.54992866516113</v>
+        <v>31.5499324798584</v>
       </c>
       <c r="C177" t="n">
         <v>33.63399887084961</v>
@@ -4970,11 +4982,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>31.24001884460449</v>
+        <v>31.24002265930176</v>
       </c>
       <c r="C178" t="n">
         <v>33.17499923706055</v>
@@ -4999,11 +5011,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>32.2127685546875</v>
+        <v>32.21277236938477</v>
       </c>
       <c r="C179" t="n">
         <v>34.20800018310547</v>
@@ -5028,11 +5040,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>42.62577819824219</v>
+        <v>42.62578582763672</v>
       </c>
       <c r="C180" t="n">
         <v>45.26599884033203</v>
@@ -5057,11 +5069,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>44.58635711669922</v>
+        <v>44.58635330200195</v>
       </c>
       <c r="C181" t="n">
         <v>47.22700119018555</v>
@@ -5086,7 +5098,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5115,11 +5127,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>53.54763412475586</v>
+        <v>53.5476188659668</v>
       </c>
       <c r="C183" t="n">
         <v>56.71900177001953</v>
@@ -5144,11 +5156,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>56.33221817016602</v>
+        <v>56.33222198486328</v>
       </c>
       <c r="C184" t="n">
         <v>59.52399826049805</v>
@@ -5173,11 +5185,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>58.71804809570312</v>
+        <v>58.71804428100586</v>
       </c>
       <c r="C185" t="n">
         <v>62.04499816894531</v>
@@ -5202,11 +5214,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>61.50040054321289</v>
+        <v>61.50039672851562</v>
       </c>
       <c r="C186" t="n">
         <v>64.98500061035156</v>
@@ -5231,11 +5243,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>61.70418930053711</v>
+        <v>61.70419692993164</v>
       </c>
       <c r="C187" t="n">
         <v>65.06999969482422</v>
@@ -5260,11 +5272,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>60.44394302368164</v>
+        <v>60.44393920898438</v>
       </c>
       <c r="C188" t="n">
         <v>63.74100112915039</v>
@@ -5289,11 +5301,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>57.35352325439453</v>
+        <v>57.353515625</v>
       </c>
       <c r="C189" t="n">
         <v>60.48199844360352</v>
@@ -5318,11 +5330,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>54.10353088378906</v>
+        <v>54.1035270690918</v>
       </c>
       <c r="C190" t="n">
         <v>56.91500091552734</v>
@@ -5347,7 +5359,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5376,7 +5388,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5405,7 +5417,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5434,11 +5446,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>56.20100784301758</v>
+        <v>56.20100402832031</v>
       </c>
       <c r="C194" t="n">
         <v>58.99200057983398</v>
@@ -5463,11 +5475,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>53.47916030883789</v>
+        <v>53.47916412353516</v>
       </c>
       <c r="C195" t="n">
         <v>56.1349983215332</v>
@@ -5492,11 +5504,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>51.38181304931641</v>
+        <v>51.38182067871094</v>
       </c>
       <c r="C196" t="n">
         <v>53.76100158691406</v>
@@ -5521,7 +5533,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5550,7 +5562,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5579,11 +5591,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>40.86619567871094</v>
+        <v>40.86619186401367</v>
       </c>
       <c r="C199" t="n">
         <v>42.6150016784668</v>
@@ -5608,11 +5620,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>47.99704360961914</v>
+        <v>47.99703598022461</v>
       </c>
       <c r="C200" t="n">
         <v>50.05099868774414</v>
@@ -5637,11 +5649,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>41.99393844604492</v>
+        <v>41.99393081665039</v>
       </c>
       <c r="C201" t="n">
         <v>43.79100036621094</v>
@@ -5666,11 +5678,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>35.23391342163086</v>
+        <v>35.23390960693359</v>
       </c>
       <c r="C202" t="n">
         <v>36.59999847412109</v>
@@ -5695,7 +5707,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5724,11 +5736,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>45.47484970092773</v>
+        <v>45.47484588623047</v>
       </c>
       <c r="C204" t="n">
         <v>47.23799896240234</v>
@@ -5753,7 +5765,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5782,11 +5794,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>48.32291793823242</v>
+        <v>48.32291412353516</v>
       </c>
       <c r="C206" t="n">
         <v>50.0099983215332</v>
@@ -5811,11 +5823,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>46.96144866943359</v>
+        <v>46.96144485473633</v>
       </c>
       <c r="C207" t="n">
         <v>48.60100173950195</v>
@@ -5840,7 +5852,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5869,11 +5881,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>50.82381439208984</v>
+        <v>50.82382202148438</v>
       </c>
       <c r="C209" t="n">
         <v>52.40800094604492</v>
@@ -5898,7 +5910,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5927,11 +5939,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>62.51461791992188</v>
+        <v>62.51461410522461</v>
       </c>
       <c r="C211" t="n">
         <v>64.28600311279297</v>
@@ -5956,7 +5968,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -5985,11 +5997,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>68.30454254150391</v>
+        <v>68.30455017089844</v>
       </c>
       <c r="C213" t="n">
         <v>70.23999786376953</v>
@@ -6014,11 +6026,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>61.13418197631836</v>
+        <v>61.13417816162109</v>
       </c>
       <c r="C214" t="n">
         <v>62.67699813842773</v>
@@ -6043,11 +6055,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>57.37406158447266</v>
+        <v>57.37406539916992</v>
       </c>
       <c r="C215" t="n">
         <v>58.82199859619141</v>
@@ -6072,11 +6084,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>69.82973480224609</v>
+        <v>69.82971954345703</v>
       </c>
       <c r="C216" t="n">
         <v>71.59200286865234</v>
@@ -6101,7 +6113,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6130,11 +6142,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>80.70523071289062</v>
+        <v>80.70522308349609</v>
       </c>
       <c r="C218" t="n">
         <v>82.51699829101562</v>
@@ -6159,7 +6171,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6188,7 +6200,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6217,7 +6229,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6246,11 +6258,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>91.39301300048828</v>
+        <v>91.39300537109375</v>
       </c>
       <c r="C222" t="n">
         <v>93.24400329589844</v>
@@ -6275,7 +6287,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6304,7 +6316,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6333,11 +6345,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>80.62165832519531</v>
+        <v>80.62164306640625</v>
       </c>
       <c r="C225" t="n">
         <v>82.10099792480469</v>
@@ -6362,7 +6374,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6391,7 +6403,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6449,11 +6461,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>71.36273956298828</v>
+        <v>71.36273193359375</v>
       </c>
       <c r="C229" t="n">
         <v>72.23000335693359</v>
@@ -6478,11 +6490,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>80.07683563232422</v>
+        <v>80.07682037353516</v>
       </c>
       <c r="C230" t="n">
         <v>81.05000305175781</v>
@@ -6507,7 +6519,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6536,11 +6548,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>72.04385375976562</v>
+        <v>72.04386138916016</v>
       </c>
       <c r="C232" t="n">
         <v>72.69999694824219</v>
@@ -6565,11 +6577,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>71.02314758300781</v>
+        <v>71.02316284179688</v>
       </c>
       <c r="C233" t="n">
         <v>71.66999816894531</v>
@@ -6594,11 +6606,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>80.06085205078125</v>
+        <v>80.06084442138672</v>
       </c>
       <c r="C234" t="n">
         <v>80.79000091552734</v>
@@ -6623,11 +6635,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>96.70149993896484</v>
+        <v>96.70150756835938</v>
       </c>
       <c r="C235" t="n">
         <v>97.33999633789062</v>
@@ -6652,7 +6664,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6681,7 +6693,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6710,7 +6722,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6739,7 +6751,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6768,11 +6780,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>155.2827606201172</v>
+        <v>155.2827453613281</v>
       </c>
       <c r="C240" t="n">
         <v>156</v>
@@ -6797,11 +6809,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>170.6734771728516</v>
+        <v>170.6734924316406</v>
       </c>
       <c r="C241" t="n">
         <v>171.1799926757812</v>
@@ -6826,7 +6838,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6855,11 +6867,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>233.1979217529297</v>
+        <v>233.1979370117188</v>
       </c>
       <c r="C243" t="n">
         <v>233.8899993896484</v>
@@ -6884,11 +6896,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>213.2830352783203</v>
+        <v>213.2830200195312</v>
       </c>
       <c r="C244" t="n">
         <v>213.6600036621094</v>
@@ -6913,11 +6925,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>257.4049987792969</v>
+        <v>257.405029296875</v>
       </c>
       <c r="C245" t="n">
         <v>257.8599853515625</v>
@@ -6942,7 +6954,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6971,7 +6983,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7000,7 +7012,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7029,7 +7041,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7058,32 +7070,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>307.2799987792969</v>
+        <v>307.1600036621094</v>
       </c>
       <c r="C250" t="n">
-        <v>307.2799987792969</v>
+        <v>307.1600036621094</v>
       </c>
       <c r="D250" t="n">
-        <v>154533200</v>
+        <v>162433300</v>
       </c>
       <c r="E250" t="n">
         <v>5.76</v>
       </c>
       <c r="F250" t="n">
-        <v>53.3472220102946</v>
+        <v>53.32638952467177</v>
       </c>
       <c r="G250" t="n">
         <v>1251321000</v>
       </c>
       <c r="H250" t="n">
-        <v>384505915352.5085</v>
+        <v>384355762942.4744</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1234960493750205</v>
+        <v>0.1298094573654562</v>
       </c>
     </row>
   </sheetData>
@@ -7115,75 +7127,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39993</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40083</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7219,13 +7231,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40084</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40174</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40577</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7261,13 +7273,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40175</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40265</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7303,13 +7315,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40266</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40356</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40774</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7336,7 +7348,7 @@
       <c r="I5" t="n">
         <v>0.271</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40774</v>
       </c>
       <c r="K5" t="n">
@@ -7349,13 +7361,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40357</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40447</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7382,7 +7394,7 @@
       <c r="I6" t="n">
         <v>0.413</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40774</v>
       </c>
       <c r="K6" t="n">
@@ -7395,13 +7407,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40448</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40538</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40577</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7428,7 +7440,7 @@
       <c r="I7" t="n">
         <v>0.537</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40774</v>
       </c>
       <c r="K7" t="n">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40539</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40629</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7474,7 +7486,7 @@
       <c r="I8" t="n">
         <v>0.5880000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40774</v>
       </c>
       <c r="K8" t="n">
@@ -7487,13 +7499,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40630</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40720</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40774</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7520,7 +7532,7 @@
       <c r="I9" t="n">
         <v>0.579</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40774</v>
       </c>
       <c r="K9" t="n">
@@ -7533,13 +7545,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40721</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40811</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7566,7 +7578,7 @@
       <c r="I10" t="n">
         <v>0.4819999999999999</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K10" t="n">
@@ -7579,13 +7591,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40812</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40902</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40942</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7612,7 +7624,7 @@
       <c r="I11" t="n">
         <v>0.331</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40942</v>
       </c>
       <c r="K11" t="n">
@@ -7625,13 +7637,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40903</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40993</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7658,7 +7670,7 @@
       <c r="I12" t="n">
         <v>0.224</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K12" t="n">
@@ -7671,13 +7683,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40994</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41084</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7704,7 +7716,7 @@
       <c r="I13" t="n">
         <v>0.135</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="K13" t="n">
@@ -7717,13 +7729,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41085</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41175</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7750,7 +7762,7 @@
       <c r="I14" t="n">
         <v>0.07900000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="K14" t="n">
@@ -7763,13 +7775,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41176</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41266</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7796,7 +7808,7 @@
       <c r="I15" t="n">
         <v>0.05600000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="K15" t="n">
@@ -7809,13 +7821,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41267</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7842,7 +7854,7 @@
       <c r="I16" t="n">
         <v>0.02900000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="K16" t="n">
@@ -7855,13 +7867,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41513</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7888,7 +7900,7 @@
       <c r="I17" t="n">
         <v>0.066</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41513</v>
       </c>
       <c r="K17" t="n">
@@ -7901,13 +7913,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7934,7 +7946,7 @@
       <c r="I18" t="n">
         <v>0.114</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K18" t="n">
@@ -7947,13 +7959,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41637</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7980,7 +7992,7 @@
       <c r="I19" t="n">
         <v>0.197</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="K19" t="n">
@@ -7993,13 +8005,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8026,7 +8038,7 @@
       <c r="I20" t="n">
         <v>0.282</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K20" t="n">
@@ -8039,13 +8051,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41877</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8072,7 +8084,7 @@
       <c r="I21" t="n">
         <v>0.362</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41877</v>
       </c>
       <c r="K21" t="n">
@@ -8085,13 +8097,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8118,7 +8130,7 @@
       <c r="I22" t="n">
         <v>0.392</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K22" t="n">
@@ -8131,13 +8143,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41911</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42038</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8164,7 +8176,7 @@
       <c r="I23" t="n">
         <v>0.405</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42038</v>
       </c>
       <c r="K23" t="n">
@@ -8177,13 +8189,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42002</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8210,7 +8222,7 @@
       <c r="I24" t="n">
         <v>0.425</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="K24" t="n">
@@ -8223,13 +8235,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42093</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42229</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8256,7 +8268,7 @@
       <c r="I25" t="n">
         <v>0.37</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42229</v>
       </c>
       <c r="K25" t="n">
@@ -8269,13 +8281,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42184</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8302,7 +8314,7 @@
       <c r="I26" t="n">
         <v>0.456</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="K26" t="n">
@@ -8315,13 +8327,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42275</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42365</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8348,7 +8360,7 @@
       <c r="I27" t="n">
         <v>0.484</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="K27" t="n">
@@ -8361,13 +8373,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42366</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42456</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42485</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8394,7 +8406,7 @@
       <c r="I28" t="n">
         <v>0.45</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42485</v>
       </c>
       <c r="K28" t="n">
@@ -8407,13 +8419,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42457</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42547</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42599</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8440,7 +8452,7 @@
       <c r="I29" t="n">
         <v>0.522</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42599</v>
       </c>
       <c r="K29" t="n">
@@ -8453,13 +8465,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42548</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42638</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8486,7 +8498,7 @@
       <c r="I30" t="n">
         <v>0.503</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="K30" t="n">
@@ -8499,13 +8511,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42639</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42729</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42765</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8532,7 +8544,7 @@
       <c r="I31" t="n">
         <v>0.556</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42765</v>
       </c>
       <c r="K31" t="n">
@@ -8545,13 +8557,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42730</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42820</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8578,7 +8590,7 @@
       <c r="I32" t="n">
         <v>0.784</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="K32" t="n">
@@ -8591,13 +8603,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42821</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42911</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42962</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8624,7 +8636,7 @@
       <c r="I33" t="n">
         <v>0.9240000000000002</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42962</v>
       </c>
       <c r="K33" t="n">
@@ -8637,13 +8649,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42912</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43002</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8670,7 +8682,7 @@
       <c r="I34" t="n">
         <v>1.098</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="K34" t="n">
@@ -8683,13 +8695,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43003</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43093</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43130</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8716,7 +8728,7 @@
       <c r="I35" t="n">
         <v>0.9110000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43130</v>
       </c>
       <c r="K35" t="n">
@@ -8729,13 +8741,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43094</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43184</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8762,7 +8774,7 @@
       <c r="I36" t="n">
         <v>1.034</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="K36" t="n">
@@ -8775,13 +8787,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43185</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43275</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43326</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8808,7 +8820,7 @@
       <c r="I37" t="n">
         <v>1.317</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43326</v>
       </c>
       <c r="K37" t="n">
@@ -8821,13 +8833,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43276</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43366</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8854,7 +8866,7 @@
       <c r="I38" t="n">
         <v>1.319</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="K38" t="n">
@@ -8867,13 +8879,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43367</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43457</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8900,7 +8912,7 @@
       <c r="I39" t="n">
         <v>1.676</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="K39" t="n">
@@ -8913,13 +8925,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8946,7 +8958,7 @@
       <c r="I40" t="n">
         <v>1.59</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K40" t="n">
@@ -8959,13 +8971,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43697</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8992,7 +9004,7 @@
       <c r="I41" t="n">
         <v>1.37</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43697</v>
       </c>
       <c r="K41" t="n">
@@ -9005,13 +9017,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9038,7 +9050,7 @@
       <c r="I42" t="n">
         <v>1.356</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="K42" t="n">
@@ -9051,13 +9063,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9084,7 +9096,7 @@
       <c r="I43" t="n">
         <v>1.348</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="K43" t="n">
@@ -9097,13 +9109,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43829</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9130,7 +9142,7 @@
       <c r="I44" t="n">
         <v>1.389</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="K44" t="n">
@@ -9143,13 +9155,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43920</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44061</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9176,7 +9188,7 @@
       <c r="I45" t="n">
         <v>1.51</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44061</v>
       </c>
       <c r="K45" t="n">
@@ -9189,13 +9201,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44011</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9222,7 +9234,7 @@
       <c r="I46" t="n">
         <v>1.76</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="K46" t="n">
@@ -9235,13 +9247,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44102</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44192</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44229</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9268,7 +9280,7 @@
       <c r="I47" t="n">
         <v>2.013</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44229</v>
       </c>
       <c r="K47" t="n">
@@ -9281,13 +9293,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44193</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44283</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9314,7 +9326,7 @@
       <c r="I48" t="n">
         <v>2.366</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K48" t="n">
@@ -9327,13 +9339,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44284</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44374</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44425</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9360,7 +9372,7 @@
       <c r="I49" t="n">
         <v>2.69</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44425</v>
       </c>
       <c r="K49" t="n">
@@ -9373,13 +9385,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44375</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44465</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9406,7 +9418,7 @@
       <c r="I50" t="n">
         <v>2.958</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="K50" t="n">
@@ -9419,13 +9431,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44466</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44556</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9452,7 +9464,7 @@
       <c r="I51" t="n">
         <v>3.206</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="K51" t="n">
@@ -9465,13 +9477,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44557</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44647</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9498,7 +9510,7 @@
       <c r="I52" t="n">
         <v>3.195</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="K52" t="n">
@@ -9511,13 +9523,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44648</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44738</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44797</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9544,7 +9556,7 @@
       <c r="I53" t="n">
         <v>3.275</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44797</v>
       </c>
       <c r="K53" t="n">
@@ -9557,13 +9569,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44739</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44829</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9590,7 +9602,7 @@
       <c r="I54" t="n">
         <v>3.487</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="K54" t="n">
@@ -9603,13 +9615,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44830</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44920</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44956</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9636,7 +9648,7 @@
       <c r="I55" t="n">
         <v>3.72</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44956</v>
       </c>
       <c r="K55" t="n">
@@ -9649,13 +9661,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44921</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45011</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9682,7 +9694,7 @@
       <c r="I56" t="n">
         <v>3.591</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="K56" t="n">
@@ -9695,13 +9707,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45012</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45102</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45153</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9728,7 +9740,7 @@
       <c r="I57" t="n">
         <v>3.321</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45153</v>
       </c>
       <c r="K57" t="n">
@@ -9741,13 +9753,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45103</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45193</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9774,7 +9786,7 @@
       <c r="I58" t="n">
         <v>2.948</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="K58" t="n">
@@ -9787,13 +9799,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45284</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9820,7 +9832,7 @@
       <c r="I59" t="n">
         <v>2.593</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="K59" t="n">
@@ -9833,13 +9845,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45285</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9866,7 +9878,7 @@
       <c r="I60" t="n">
         <v>2.726</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="K60" t="n">
@@ -9879,13 +9891,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9912,7 +9924,7 @@
       <c r="I61" t="n">
         <v>2.9</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="K61" t="n">
@@ -9925,13 +9937,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9958,7 +9970,7 @@
       <c r="I62" t="n">
         <v>3.094</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="K62" t="n">
@@ -9971,13 +9983,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10004,7 +10016,7 @@
       <c r="I63" t="n">
         <v>3.292</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K63" t="n">
@@ -10017,13 +10029,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45656</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10050,7 +10062,7 @@
       <c r="I64" t="n">
         <v>3.588</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K64" t="n">
@@ -10063,13 +10075,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10096,7 +10108,7 @@
       <c r="I65" t="n">
         <v>4.15</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="K65" t="n">
@@ -10109,13 +10121,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10142,7 +10154,7 @@
       <c r="I66" t="n">
         <v>4.53</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="K66" t="n">
@@ -10155,13 +10167,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45929</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10188,7 +10200,7 @@
       <c r="I67" t="n">
         <v>4.87</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="K67" t="n">
@@ -10201,13 +10213,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46020</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10234,7 +10246,7 @@
       <c r="I68" t="n">
         <v>5.29</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K68" t="n">
@@ -10247,13 +10259,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46111</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46201</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10280,7 +10292,7 @@
       <c r="I69" t="n">
         <v>5.76</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="K69" t="n">
@@ -10317,52 +10329,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C2" t="n">
@@ -10391,10 +10403,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40571</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40577</v>
       </c>
       <c r="C3" t="n">
@@ -10423,10 +10435,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C4" t="n">
@@ -10455,10 +10467,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40767</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40774</v>
       </c>
       <c r="C5" t="n">
@@ -10487,10 +10499,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C6" t="n">
@@ -10519,10 +10531,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40938</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40942</v>
       </c>
       <c r="C7" t="n">
@@ -10551,10 +10563,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C8" t="n">
@@ -10583,10 +10595,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41135</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="C9" t="n">
@@ -10615,10 +10627,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C10" t="n">
@@ -10647,10 +10659,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41299</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="C11" t="n">
@@ -10679,10 +10691,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41397</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="C12" t="n">
@@ -10711,10 +10723,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41506</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41513</v>
       </c>
       <c r="C13" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C14" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="C15" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41761</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C16" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41871</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41877</v>
       </c>
       <c r="C17" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41940</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C18" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42032</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42038</v>
       </c>
       <c r="C19" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42121</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="C20" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42221</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42229</v>
       </c>
       <c r="C21" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="C22" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="C23" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42481</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42485</v>
       </c>
       <c r="C24" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42592</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42599</v>
       </c>
       <c r="C25" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42663</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="C26" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42761</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42765</v>
       </c>
       <c r="C27" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42845</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="C28" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42957</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42962</v>
       </c>
       <c r="C29" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43027</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="C30" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43125</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43130</v>
       </c>
       <c r="C31" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43209</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="C32" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43321</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43326</v>
       </c>
       <c r="C33" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43395</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="C34" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43493</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="C35" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43581</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C36" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43692</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43697</v>
       </c>
       <c r="C37" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="C38" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="C39" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43945</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="C40" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44056</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44061</v>
       </c>
       <c r="C41" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="C42" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44229</v>
       </c>
       <c r="C43" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44312</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C44" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44420</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44425</v>
       </c>
       <c r="C45" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44491</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="C46" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="C47" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="C48" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44795</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44797</v>
       </c>
       <c r="C49" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44854</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="C50" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44952</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44956</v>
       </c>
       <c r="C51" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45036</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="C52" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45148</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45153</v>
       </c>
       <c r="C53" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45218</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="C54" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45316</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="C55" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45407</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="C56" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45526</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="C57" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45589</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="C58" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45686</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C59" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45770</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C60" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45876</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="C61" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45952</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="C62" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46049</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="C63" t="n">
@@ -12343,10 +12355,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C64" t="n">
@@ -12375,10 +12387,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46238</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="C65" t="n">
@@ -12425,12 +12437,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/LRCX.xlsx
+++ b/salidas/empresas/LRCX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>3.93491530418396</v>
+        <v>3.934917688369751</v>
       </c>
       <c r="C2" t="n">
         <v>4.64300012588501</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>3.652698755264282</v>
+        <v>3.652699947357178</v>
       </c>
       <c r="C3" t="n">
         <v>4.309999942779541</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>3.644224643707275</v>
+        <v>3.644225835800171</v>
       </c>
       <c r="C4" t="n">
         <v>4.300000190734863</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>4.142552375793457</v>
+        <v>4.142551422119141</v>
       </c>
       <c r="C5" t="n">
         <v>4.888000011444092</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>3.795926570892334</v>
+        <v>3.79592490196228</v>
       </c>
       <c r="C6" t="n">
         <v>4.479000091552734</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>3.959491968154907</v>
+        <v>3.959492206573486</v>
       </c>
       <c r="C7" t="n">
         <v>4.671999931335449</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>3.525575876235962</v>
+        <v>3.52557635307312</v>
       </c>
       <c r="C8" t="n">
         <v>4.159999847412109</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>3.621342658996582</v>
+        <v>3.621341705322266</v>
       </c>
       <c r="C9" t="n">
         <v>4.27299976348877</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>3.841691970825195</v>
+        <v>3.841689825057983</v>
       </c>
       <c r="C10" t="n">
         <v>4.532999992370605</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>4.190860271453857</v>
+        <v>4.190857887268066</v>
       </c>
       <c r="C11" t="n">
         <v>4.945000171661377</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>4.457820892333984</v>
+        <v>4.457818508148193</v>
       </c>
       <c r="C12" t="n">
         <v>5.260000228881836</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>4.290016651153564</v>
+        <v>4.290015697479248</v>
       </c>
       <c r="C13" t="n">
         <v>5.061999797821045</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>3.882370710372925</v>
+        <v>3.882371425628662</v>
       </c>
       <c r="C14" t="n">
         <v>4.580999851226807</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>3.784908294677734</v>
+        <v>3.784910202026367</v>
       </c>
       <c r="C15" t="n">
         <v>4.466000080108643</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>4.01203727722168</v>
+        <v>4.012038707733154</v>
       </c>
       <c r="C16" t="n">
         <v>4.734000205993652</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>4.55782413482666</v>
+        <v>4.557822227478027</v>
       </c>
       <c r="C17" t="n">
         <v>5.377999782562256</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>4.552739143371582</v>
+        <v>4.552737236022949</v>
       </c>
       <c r="C18" t="n">
         <v>5.372000217437744</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>4.356118679046631</v>
+        <v>4.356121063232422</v>
       </c>
       <c r="C19" t="n">
         <v>5.139999866485596</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>4.901907444000244</v>
+        <v>4.901907920837402</v>
       </c>
       <c r="C20" t="n">
         <v>5.783999919891357</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>4.545111179351807</v>
+        <v>4.545112133026123</v>
       </c>
       <c r="C21" t="n">
         <v>5.36299991607666</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>4.254421710968018</v>
+        <v>4.254421234130859</v>
       </c>
       <c r="C23" t="n">
         <v>5.019999980926514</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>3.885761022567749</v>
+        <v>3.885761260986328</v>
       </c>
       <c r="C24" t="n">
         <v>4.585000038146973</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>3.663717985153198</v>
+        <v>3.663715839385986</v>
       </c>
       <c r="C25" t="n">
         <v>4.322999954223633</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>3.253530025482178</v>
+        <v>3.253530263900757</v>
       </c>
       <c r="C26" t="n">
         <v>3.83899998664856</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>3.410316944122314</v>
+        <v>3.410316228866577</v>
       </c>
       <c r="C27" t="n">
         <v>4.02400016784668</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>3.239123106002808</v>
+        <v>3.239122867584229</v>
       </c>
       <c r="C28" t="n">
         <v>3.822000026702881</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>3.461166620254517</v>
+        <v>3.461166381835938</v>
       </c>
       <c r="C29" t="n">
         <v>4.084000110626221</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>3.449301719665527</v>
+        <v>3.449301242828369</v>
       </c>
       <c r="C30" t="n">
         <v>4.070000171661377</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>2.787408113479614</v>
+        <v>2.787408351898193</v>
       </c>
       <c r="C32" t="n">
         <v>3.289000034332275</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>3.115389108657837</v>
+        <v>3.115387916564941</v>
       </c>
       <c r="C33" t="n">
         <v>3.676000118255615</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>1.7119380235672</v>
+        <v>1.711938261985779</v>
       </c>
       <c r="C36" t="n">
         <v>2.019999980926514</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>1.803467988967896</v>
+        <v>1.803467750549316</v>
       </c>
       <c r="C37" t="n">
         <v>2.128000020980835</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>1.712786078453064</v>
+        <v>1.712785482406616</v>
       </c>
       <c r="C38" t="n">
         <v>2.020999908447266</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>1.657698631286621</v>
+        <v>1.6576988697052</v>
       </c>
       <c r="C39" t="n">
         <v>1.955999970436096</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>2.36281418800354</v>
+        <v>2.362813949584961</v>
       </c>
       <c r="C41" t="n">
         <v>2.788000106811523</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>2.219587564468384</v>
+        <v>2.219587802886963</v>
       </c>
       <c r="C42" t="n">
         <v>2.61899995803833</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>2.203485012054443</v>
+        <v>2.203484773635864</v>
       </c>
       <c r="C43" t="n">
         <v>2.599999904632568</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>2.547567844390869</v>
+        <v>2.54756760597229</v>
       </c>
       <c r="C44" t="n">
         <v>3.00600004196167</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>2.601807117462158</v>
+        <v>2.601806402206421</v>
       </c>
       <c r="C45" t="n">
         <v>3.069999933242798</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>2.895039558410645</v>
+        <v>2.895039319992065</v>
       </c>
       <c r="C46" t="n">
         <v>3.415999889373779</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>2.857750415802002</v>
+        <v>2.857750177383423</v>
       </c>
       <c r="C47" t="n">
         <v>3.371999979019165</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>2.880631685256958</v>
+        <v>2.880632400512695</v>
       </c>
       <c r="C48" t="n">
         <v>3.398999929428101</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>3.323024749755859</v>
+        <v>3.323024988174438</v>
       </c>
       <c r="C49" t="n">
         <v>3.921000003814697</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>2.79757833480835</v>
+        <v>2.797579288482666</v>
       </c>
       <c r="C50" t="n">
         <v>3.301000118255615</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>2.873852491378784</v>
+        <v>2.873852014541626</v>
       </c>
       <c r="C51" t="n">
         <v>3.391000032424927</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>3.162847995758057</v>
+        <v>3.162848472595215</v>
       </c>
       <c r="C52" t="n">
         <v>3.732000112533569</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>3.435741662979126</v>
+        <v>3.43574070930481</v>
       </c>
       <c r="C53" t="n">
         <v>4.053999900817871</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>3.20861291885376</v>
+        <v>3.208613395690918</v>
       </c>
       <c r="C54" t="n">
         <v>3.78600001335144</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>3.225563526153564</v>
+        <v>3.225563287734985</v>
       </c>
       <c r="C55" t="n">
         <v>3.805999994277954</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>3.575577259063721</v>
+        <v>3.575577735900879</v>
       </c>
       <c r="C56" t="n">
         <v>4.218999862670898</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>3.060300827026367</v>
+        <v>3.060301542282104</v>
       </c>
       <c r="C57" t="n">
         <v>3.611000061035156</v>
@@ -1562,7 +1562,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>3.546763181686401</v>
+        <v>3.546765089035034</v>
       </c>
       <c r="C58" t="n">
         <v>4.184999942779541</v>
@@ -1581,7 +1581,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>3.880675315856934</v>
+        <v>3.88067626953125</v>
       </c>
       <c r="C59" t="n">
         <v>4.578999996185303</v>
@@ -1600,7 +1600,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>3.847624778747559</v>
+        <v>3.847623109817505</v>
       </c>
       <c r="C60" t="n">
         <v>4.539999961853027</v>
@@ -1625,7 +1625,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>4.38832426071167</v>
+        <v>4.388323307037354</v>
       </c>
       <c r="C61" t="n">
         <v>5.177999973297119</v>
@@ -1650,7 +1650,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>4.2281494140625</v>
+        <v>4.228147506713867</v>
       </c>
       <c r="C62" t="n">
         <v>4.988999843597412</v>
@@ -1675,7 +1675,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>4.652742862701416</v>
+        <v>4.652742385864258</v>
       </c>
       <c r="C63" t="n">
         <v>5.489999771118164</v>
@@ -1700,7 +1700,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>4.801901817321777</v>
+        <v>4.801902770996094</v>
       </c>
       <c r="C64" t="n">
         <v>5.665999889373779</v>
@@ -1725,7 +1725,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>4.094244480133057</v>
+        <v>4.094245433807373</v>
       </c>
       <c r="C65" t="n">
         <v>4.830999851226807</v>
@@ -1750,7 +1750,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>3.982376098632812</v>
+        <v>3.982373237609863</v>
       </c>
       <c r="C66" t="n">
         <v>4.698999881744385</v>
@@ -1775,7 +1775,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>3.752703905105591</v>
+        <v>3.752705574035645</v>
       </c>
       <c r="C67" t="n">
         <v>4.427999973297119</v>
@@ -1800,7 +1800,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>3.464556455612183</v>
+        <v>3.464556932449341</v>
       </c>
       <c r="C68" t="n">
         <v>4.087999820709229</v>
@@ -1825,7 +1825,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>3.149288177490234</v>
+        <v>3.149287939071655</v>
       </c>
       <c r="C69" t="n">
         <v>3.716000080108643</v>
@@ -1854,7 +1854,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>3.218782424926758</v>
+        <v>3.218783378601074</v>
       </c>
       <c r="C70" t="n">
         <v>3.79800009727478</v>
@@ -1883,7 +1883,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>3.643377065658569</v>
+        <v>3.64337682723999</v>
       </c>
       <c r="C71" t="n">
         <v>4.298999786376953</v>
@@ -1912,7 +1912,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>3.455233335494995</v>
+        <v>3.455233573913574</v>
       </c>
       <c r="C72" t="n">
         <v>4.077000141143799</v>
@@ -1941,7 +1941,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>3.137422800064087</v>
+        <v>3.137423515319824</v>
       </c>
       <c r="C73" t="n">
         <v>3.70199990272522</v>
@@ -1970,7 +1970,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>3.609476804733276</v>
+        <v>3.609478235244751</v>
       </c>
       <c r="C74" t="n">
         <v>4.258999824523926</v>
@@ -1999,7 +1999,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>3.534050703048706</v>
+        <v>3.534049987792969</v>
       </c>
       <c r="C75" t="n">
         <v>4.170000076293945</v>
@@ -2057,7 +2057,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>3.531508684158325</v>
+        <v>3.531508922576904</v>
       </c>
       <c r="C77" t="n">
         <v>4.166999816894531</v>
@@ -2086,7 +2086,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>3.161153078079224</v>
+        <v>3.161153554916382</v>
       </c>
       <c r="C78" t="n">
         <v>3.730000019073486</v>
@@ -2115,7 +2115,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>3.198442220687866</v>
+        <v>3.19844388961792</v>
       </c>
       <c r="C79" t="n">
         <v>3.773999929428101</v>
@@ -2144,7 +2144,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>2.916226863861084</v>
+        <v>2.916228055953979</v>
       </c>
       <c r="C80" t="n">
         <v>3.440999984741211</v>
@@ -2173,7 +2173,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>2.892497777938843</v>
+        <v>2.892498016357422</v>
       </c>
       <c r="C81" t="n">
         <v>3.413000106811523</v>
@@ -2202,7 +2202,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>2.693336248397827</v>
+        <v>2.693336725234985</v>
       </c>
       <c r="C82" t="n">
         <v>3.177999973297119</v>
@@ -2231,7 +2231,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>3.000129461288452</v>
+        <v>3.00012993812561</v>
       </c>
       <c r="C83" t="n">
         <v>3.539999961853027</v>
@@ -2260,7 +2260,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>2.976399660110474</v>
+        <v>2.976399898529053</v>
       </c>
       <c r="C84" t="n">
         <v>3.51200008392334</v>
@@ -2289,7 +2289,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>3.061996459960938</v>
+        <v>3.061996221542358</v>
       </c>
       <c r="C85" t="n">
         <v>3.61299991607666</v>
@@ -2318,7 +2318,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>3.486591100692749</v>
+        <v>3.486590623855591</v>
       </c>
       <c r="C86" t="n">
         <v>4.113999843597412</v>
@@ -2347,7 +2347,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>3.584899663925171</v>
+        <v>3.584900379180908</v>
       </c>
       <c r="C87" t="n">
         <v>4.230000019073486</v>
@@ -2405,7 +2405,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>3.917117357254028</v>
+        <v>3.917116165161133</v>
       </c>
       <c r="C89" t="n">
         <v>4.622000217437744</v>
@@ -2434,7 +2434,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>3.96457839012146</v>
+        <v>3.964578628540039</v>
       </c>
       <c r="C90" t="n">
         <v>4.677999973297119</v>
@@ -2463,7 +2463,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>3.757791042327881</v>
+        <v>3.757789850234985</v>
       </c>
       <c r="C91" t="n">
         <v>4.434000015258789</v>
@@ -2492,7 +2492,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>4.171365737915039</v>
+        <v>4.171366214752197</v>
       </c>
       <c r="C92" t="n">
         <v>4.921999931335449</v>
@@ -2521,7 +2521,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>3.955255746841431</v>
+        <v>3.955256462097168</v>
       </c>
       <c r="C93" t="n">
         <v>4.666999816894531</v>
@@ -2550,7 +2550,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>4.339169025421143</v>
+        <v>4.339169502258301</v>
       </c>
       <c r="C94" t="n">
         <v>5.119999885559082</v>
@@ -2579,7 +2579,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>4.599350452423096</v>
+        <v>4.599351406097412</v>
       </c>
       <c r="C95" t="n">
         <v>5.427000045776367</v>
@@ -2608,7 +2608,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>4.416291236877441</v>
+        <v>4.416292667388916</v>
       </c>
       <c r="C96" t="n">
         <v>5.210999965667725</v>
@@ -2637,7 +2637,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>4.614606380462646</v>
+        <v>4.61460542678833</v>
       </c>
       <c r="C97" t="n">
         <v>5.445000171661377</v>
@@ -2666,7 +2666,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>4.289167881011963</v>
+        <v>4.289167404174805</v>
       </c>
       <c r="C98" t="n">
         <v>5.060999870300293</v>
@@ -2695,7 +2695,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>4.384088039398193</v>
+        <v>4.384088516235352</v>
       </c>
       <c r="C99" t="n">
         <v>5.172999858856201</v>
@@ -2724,7 +2724,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>4.661218166351318</v>
+        <v>4.661219596862793</v>
       </c>
       <c r="C100" t="n">
         <v>5.5</v>
@@ -2753,7 +2753,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>4.8824143409729</v>
+        <v>4.882411956787109</v>
       </c>
       <c r="C101" t="n">
         <v>5.761000156402588</v>
@@ -2782,7 +2782,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>5.25785493850708</v>
+        <v>5.257853031158447</v>
       </c>
       <c r="C102" t="n">
         <v>6.203999996185303</v>
@@ -2840,7 +2840,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>5.948934555053711</v>
+        <v>5.948935031890869</v>
       </c>
       <c r="C104" t="n">
         <v>7</v>
@@ -2869,7 +2869,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>6.111253261566162</v>
+        <v>6.111254692077637</v>
       </c>
       <c r="C105" t="n">
         <v>7.190999984741211</v>
@@ -2898,7 +2898,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>6.364280223846436</v>
+        <v>6.364279270172119</v>
       </c>
       <c r="C106" t="n">
         <v>7.46999979019165</v>
@@ -2927,7 +2927,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>6.633504867553711</v>
+        <v>6.633504390716553</v>
       </c>
       <c r="C107" t="n">
         <v>7.785999774932861</v>
@@ -2956,7 +2956,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>7.040749549865723</v>
+        <v>7.040749073028564</v>
       </c>
       <c r="C108" t="n">
         <v>8.263999938964844</v>
@@ -2985,7 +2985,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>6.774062633514404</v>
+        <v>6.774060249328613</v>
       </c>
       <c r="C109" t="n">
         <v>7.934000015258789</v>
@@ -3043,7 +3043,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>7.04044771194458</v>
+        <v>7.040448665618896</v>
       </c>
       <c r="C111" t="n">
         <v>8.246000289916992</v>
@@ -3159,7 +3159,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>6.986424922943115</v>
+        <v>6.986425876617432</v>
       </c>
       <c r="C115" t="n">
         <v>8.135000228881836</v>
@@ -3188,7 +3188,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>6.601677894592285</v>
+        <v>6.601676940917969</v>
       </c>
       <c r="C116" t="n">
         <v>7.686999797821045</v>
@@ -3217,7 +3217,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>6.249565124511719</v>
+        <v>6.249564170837402</v>
       </c>
       <c r="C117" t="n">
         <v>7.276999950408936</v>
@@ -3246,7 +3246,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>5.63416576385498</v>
+        <v>5.634166240692139</v>
       </c>
       <c r="C118" t="n">
         <v>6.532999992370605</v>
@@ -3333,7 +3333,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>6.875867366790771</v>
+        <v>6.87586784362793</v>
       </c>
       <c r="C121" t="n">
         <v>7.941999912261963</v>
@@ -3362,7 +3362,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>6.215291023254395</v>
+        <v>6.215291500091553</v>
       </c>
       <c r="C122" t="n">
         <v>7.178999900817871</v>
@@ -3391,7 +3391,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>6.346021175384521</v>
+        <v>6.346022129058838</v>
       </c>
       <c r="C123" t="n">
         <v>7.329999923706055</v>
@@ -3420,7 +3420,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>7.180158138275146</v>
+        <v>7.180159568786621</v>
       </c>
       <c r="C124" t="n">
         <v>8.260000228881836</v>
@@ -3449,7 +3449,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>6.641211986541748</v>
+        <v>6.64121150970459</v>
       </c>
       <c r="C125" t="n">
         <v>7.639999866485596</v>
@@ -3478,7 +3478,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>7.198412418365479</v>
+        <v>7.198413372039795</v>
       </c>
       <c r="C126" t="n">
         <v>8.281000137329102</v>
@@ -3507,7 +3507,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>7.333547115325928</v>
+        <v>7.333549022674561</v>
       </c>
       <c r="C127" t="n">
         <v>8.406000137329102</v>
@@ -3536,7 +3536,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>7.831699848175049</v>
+        <v>7.831696510314941</v>
       </c>
       <c r="C128" t="n">
         <v>8.97700023651123</v>
@@ -3565,7 +3565,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>8.141407012939453</v>
+        <v>8.14140796661377</v>
       </c>
       <c r="C129" t="n">
         <v>9.331999778747559</v>
@@ -3594,7 +3594,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>8.289946556091309</v>
+        <v>8.289944648742676</v>
       </c>
       <c r="C130" t="n">
         <v>9.470999717712402</v>
@@ -3623,7 +3623,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>8.478137969970703</v>
+        <v>8.478135108947754</v>
       </c>
       <c r="C131" t="n">
         <v>9.685999870300293</v>
@@ -3652,7 +3652,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>9.279911041259766</v>
+        <v>9.279911994934082</v>
       </c>
       <c r="C132" t="n">
         <v>10.60200023651123</v>
@@ -3681,7 +3681,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>9.294712066650391</v>
+        <v>9.294713020324707</v>
       </c>
       <c r="C133" t="n">
         <v>10.57299995422363</v>
@@ -3710,7 +3710,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>10.09732532501221</v>
+        <v>10.09732723236084</v>
       </c>
       <c r="C134" t="n">
         <v>11.48600006103516</v>
@@ -3739,7 +3739,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>10.42083358764648</v>
+        <v>10.42083549499512</v>
       </c>
       <c r="C135" t="n">
         <v>11.85400009155273</v>
@@ -3768,7 +3768,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>11.32707977294922</v>
+        <v>11.32708168029785</v>
       </c>
       <c r="C136" t="n">
         <v>12.83600044250488</v>
@@ -3797,7 +3797,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>12.78223037719727</v>
+        <v>12.7822322845459</v>
       </c>
       <c r="C137" t="n">
         <v>14.48499965667725</v>
@@ -3826,7 +3826,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>13.69291210174561</v>
+        <v>13.69291591644287</v>
       </c>
       <c r="C138" t="n">
         <v>15.51700019836426</v>
@@ -3855,7 +3855,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>12.5159158706665</v>
+        <v>12.51591682434082</v>
       </c>
       <c r="C139" t="n">
         <v>14.14299964904785</v>
@@ -3884,7 +3884,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>14.11149120330811</v>
+        <v>14.11149024963379</v>
       </c>
       <c r="C140" t="n">
         <v>15.94600009918213</v>
@@ -3913,7 +3913,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>14.68847560882568</v>
+        <v>14.68848037719727</v>
       </c>
       <c r="C141" t="n">
         <v>16.59799957275391</v>
@@ -3942,7 +3942,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>16.41867637634277</v>
+        <v>16.41867256164551</v>
       </c>
       <c r="C142" t="n">
         <v>18.50399971008301</v>
@@ -3971,7 +3971,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>18.50650215148926</v>
+        <v>18.50650405883789</v>
       </c>
       <c r="C143" t="n">
         <v>20.85700035095215</v>
@@ -4000,7 +4000,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>17.06552314758301</v>
+        <v>17.06552124023438</v>
       </c>
       <c r="C144" t="n">
         <v>19.23299980163574</v>
@@ -4029,7 +4029,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>16.37791633605957</v>
+        <v>16.3779182434082</v>
       </c>
       <c r="C145" t="n">
         <v>18.4069995880127</v>
@@ -4087,7 +4087,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>17.07104682922363</v>
+        <v>17.07104110717773</v>
       </c>
       <c r="C147" t="n">
         <v>19.18600082397461</v>
@@ -4116,7 +4116,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>18.1220817565918</v>
+        <v>18.12207794189453</v>
       </c>
       <c r="C148" t="n">
         <v>20.31599998474121</v>
@@ -4145,7 +4145,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>16.50754547119141</v>
+        <v>16.50753974914551</v>
       </c>
       <c r="C149" t="n">
         <v>18.50600051879883</v>
@@ -4174,7 +4174,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>17.67786598205566</v>
+        <v>17.67786026000977</v>
       </c>
       <c r="C150" t="n">
         <v>19.81800079345703</v>
@@ -4203,7 +4203,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>15.50174331665039</v>
+        <v>15.50174045562744</v>
       </c>
       <c r="C151" t="n">
         <v>17.28499984741211</v>
@@ -4232,7 +4232,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>17.09720420837402</v>
+        <v>17.09720802307129</v>
       </c>
       <c r="C152" t="n">
         <v>19.06399917602539</v>
@@ -4261,7 +4261,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>15.52326488494873</v>
+        <v>15.52326679229736</v>
       </c>
       <c r="C153" t="n">
         <v>17.30900001525879</v>
@@ -4290,7 +4290,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>13.69944381713867</v>
+        <v>13.6994457244873</v>
       </c>
       <c r="C154" t="n">
         <v>15.17000007629395</v>
@@ -4319,7 +4319,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>12.79909420013428</v>
+        <v>12.79909229278564</v>
       </c>
       <c r="C155" t="n">
         <v>14.17300033569336</v>
@@ -4348,7 +4348,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>14.17445850372314</v>
+        <v>14.17445468902588</v>
       </c>
       <c r="C156" t="n">
         <v>15.69600009918213</v>
@@ -4377,7 +4377,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>12.38157367706299</v>
+        <v>12.38157653808594</v>
       </c>
       <c r="C157" t="n">
         <v>13.61699962615967</v>
@@ -4406,7 +4406,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>15.41945552825928</v>
+        <v>15.41945743560791</v>
       </c>
       <c r="C158" t="n">
         <v>16.95800018310547</v>
@@ -4435,7 +4435,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>16.01140022277832</v>
+        <v>16.01139259338379</v>
       </c>
       <c r="C159" t="n">
         <v>17.60899925231934</v>
@@ -4522,7 +4522,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>15.97433948516846</v>
+        <v>15.97433757781982</v>
       </c>
       <c r="C162" t="n">
         <v>17.46100044250488</v>
@@ -4551,7 +4551,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>17.28414344787598</v>
+        <v>17.28414726257324</v>
       </c>
       <c r="C163" t="n">
         <v>18.78400039672852</v>
@@ -4580,7 +4580,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>19.1953010559082</v>
+        <v>19.19529724121094</v>
       </c>
       <c r="C164" t="n">
         <v>20.86100006103516</v>
@@ -4609,7 +4609,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>19.37013626098633</v>
+        <v>19.37013244628906</v>
       </c>
       <c r="C165" t="n">
         <v>21.05100059509277</v>
@@ -4638,7 +4638,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>21.37247085571289</v>
+        <v>21.37247276306152</v>
       </c>
       <c r="C166" t="n">
         <v>23.11100006103516</v>
@@ -4667,7 +4667,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>25.06509780883789</v>
+        <v>25.06509399414062</v>
       </c>
       <c r="C167" t="n">
         <v>27.10400009155273</v>
@@ -4754,7 +4754,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>27.69654655456543</v>
+        <v>27.6965446472168</v>
       </c>
       <c r="C170" t="n">
         <v>29.82099914550781</v>
@@ -4783,7 +4783,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>27.25259971618652</v>
+        <v>27.25259590148926</v>
       </c>
       <c r="C171" t="n">
         <v>29.3430004119873</v>
@@ -4812,7 +4812,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>22.42395401000977</v>
+        <v>22.4239559173584</v>
       </c>
       <c r="C172" t="n">
         <v>24</v>
@@ -4841,7 +4841,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>23.85161399841309</v>
+        <v>23.85161018371582</v>
       </c>
       <c r="C173" t="n">
         <v>25.52799987792969</v>
@@ -4870,7 +4870,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>25.56985473632812</v>
+        <v>25.56984901428223</v>
       </c>
       <c r="C174" t="n">
         <v>27.36700057983398</v>
@@ -4899,7 +4899,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>30.34173774719238</v>
+        <v>30.34173583984375</v>
       </c>
       <c r="C175" t="n">
         <v>32.34600067138672</v>
@@ -4928,7 +4928,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>35.37899780273438</v>
+        <v>35.37899017333984</v>
       </c>
       <c r="C176" t="n">
         <v>37.71599960327148</v>
@@ -4957,7 +4957,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.5499324798584</v>
+        <v>31.54992866516113</v>
       </c>
       <c r="C177" t="n">
         <v>33.63399887084961</v>
@@ -4986,7 +4986,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>31.24002265930176</v>
+        <v>31.24001693725586</v>
       </c>
       <c r="C178" t="n">
         <v>33.17499923706055</v>
@@ -5044,7 +5044,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>42.62578582763672</v>
+        <v>42.62579727172852</v>
       </c>
       <c r="C180" t="n">
         <v>45.26599884033203</v>
@@ -5073,7 +5073,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>44.58635330200195</v>
+        <v>44.58636093139648</v>
       </c>
       <c r="C181" t="n">
         <v>47.22700119018555</v>
@@ -5102,7 +5102,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>45.68906021118164</v>
+        <v>45.68904113769531</v>
       </c>
       <c r="C182" t="n">
         <v>48.39500045776367</v>
@@ -5131,7 +5131,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>53.5476188659668</v>
+        <v>53.54763031005859</v>
       </c>
       <c r="C183" t="n">
         <v>56.71900177001953</v>
@@ -5189,7 +5189,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>58.71804428100586</v>
+        <v>58.71803665161133</v>
       </c>
       <c r="C185" t="n">
         <v>62.04499816894531</v>
@@ -5218,7 +5218,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>61.50039672851562</v>
+        <v>61.50038909912109</v>
       </c>
       <c r="C186" t="n">
         <v>64.98500061035156</v>
@@ -5247,7 +5247,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>61.70419692993164</v>
+        <v>61.70419311523438</v>
       </c>
       <c r="C187" t="n">
         <v>65.06999969482422</v>
@@ -5276,7 +5276,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>60.44393920898438</v>
+        <v>60.44395065307617</v>
       </c>
       <c r="C188" t="n">
         <v>63.74100112915039</v>
@@ -5305,7 +5305,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>57.353515625</v>
+        <v>57.35350799560547</v>
       </c>
       <c r="C189" t="n">
         <v>60.48199844360352</v>
@@ -5334,7 +5334,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>54.1035270690918</v>
+        <v>54.103515625</v>
       </c>
       <c r="C190" t="n">
         <v>56.91500091552734</v>
@@ -5363,7 +5363,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>53.57307815551758</v>
+        <v>53.57308197021484</v>
       </c>
       <c r="C191" t="n">
         <v>56.35699844360352</v>
@@ -5450,7 +5450,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>56.20100402832031</v>
+        <v>56.20100021362305</v>
       </c>
       <c r="C194" t="n">
         <v>58.99200057983398</v>
@@ -5508,7 +5508,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>51.38182067871094</v>
+        <v>51.3818244934082</v>
       </c>
       <c r="C196" t="n">
         <v>53.76100158691406</v>
@@ -5537,7 +5537,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>44.51479339599609</v>
+        <v>44.5147819519043</v>
       </c>
       <c r="C197" t="n">
         <v>46.57600021362305</v>
@@ -5566,7 +5566,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>49.70162200927734</v>
+        <v>49.70161056518555</v>
       </c>
       <c r="C198" t="n">
         <v>52.00299835205078</v>
@@ -5653,7 +5653,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>41.99393081665039</v>
+        <v>41.99393463134766</v>
       </c>
       <c r="C201" t="n">
         <v>43.79100036621094</v>
@@ -5682,7 +5682,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>35.23390960693359</v>
+        <v>35.23391342163086</v>
       </c>
       <c r="C202" t="n">
         <v>36.59999847412109</v>
@@ -5711,7 +5711,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>38.96715927124023</v>
+        <v>38.9671630859375</v>
       </c>
       <c r="C203" t="n">
         <v>40.47800064086914</v>
@@ -5740,7 +5740,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>45.47484588623047</v>
+        <v>45.47484970092773</v>
       </c>
       <c r="C204" t="n">
         <v>47.23799896240234</v>
@@ -5769,7 +5769,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>40.61211776733398</v>
+        <v>40.61212539672852</v>
       </c>
       <c r="C205" t="n">
         <v>42.02999877929688</v>
@@ -5798,7 +5798,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>48.32291412353516</v>
+        <v>48.32292556762695</v>
       </c>
       <c r="C206" t="n">
         <v>50.0099983215332</v>
@@ -5827,7 +5827,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>46.96144485473633</v>
+        <v>46.96145629882812</v>
       </c>
       <c r="C207" t="n">
         <v>48.60100173950195</v>
@@ -5856,7 +5856,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>51.40956115722656</v>
+        <v>51.4095573425293</v>
       </c>
       <c r="C208" t="n">
         <v>53.01200103759766</v>
@@ -5885,7 +5885,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>50.82382202148438</v>
+        <v>50.82381820678711</v>
       </c>
       <c r="C209" t="n">
         <v>52.40800094604492</v>
@@ -5943,7 +5943,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>62.51461410522461</v>
+        <v>62.51461029052734</v>
       </c>
       <c r="C211" t="n">
         <v>64.28600311279297</v>
@@ -5972,7 +5972,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>69.86920928955078</v>
+        <v>69.86922454833984</v>
       </c>
       <c r="C212" t="n">
         <v>71.8489990234375</v>
@@ -6001,7 +6001,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>68.30455017089844</v>
+        <v>68.30454254150391</v>
       </c>
       <c r="C213" t="n">
         <v>70.23999786376953</v>
@@ -6030,7 +6030,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>61.13417816162109</v>
+        <v>61.13417434692383</v>
       </c>
       <c r="C214" t="n">
         <v>62.67699813842773</v>
@@ -6088,7 +6088,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>69.82971954345703</v>
+        <v>69.82972717285156</v>
       </c>
       <c r="C216" t="n">
         <v>71.59200286865234</v>
@@ -6146,7 +6146,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>80.70522308349609</v>
+        <v>80.70524597167969</v>
       </c>
       <c r="C218" t="n">
         <v>82.51699829101562</v>
@@ -6204,7 +6204,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>95.22832489013672</v>
+        <v>95.22833251953125</v>
       </c>
       <c r="C220" t="n">
         <v>97.15699768066406</v>
@@ -6291,7 +6291,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>104.5662994384766</v>
+        <v>104.5663070678711</v>
       </c>
       <c r="C223" t="n">
         <v>106.4850006103516</v>
@@ -6320,7 +6320,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>90.46406555175781</v>
+        <v>90.46405792236328</v>
       </c>
       <c r="C224" t="n">
         <v>92.12400054931641</v>
@@ -6349,7 +6349,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>80.62164306640625</v>
+        <v>80.62165832519531</v>
       </c>
       <c r="C225" t="n">
         <v>82.10099792480469</v>
@@ -6407,7 +6407,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>73.23239898681641</v>
+        <v>73.23240661621094</v>
       </c>
       <c r="C227" t="n">
         <v>74.34999847412109</v>
@@ -6465,7 +6465,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>71.36273193359375</v>
+        <v>71.36271667480469</v>
       </c>
       <c r="C229" t="n">
         <v>72.23000335693359</v>
@@ -6494,7 +6494,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>80.07682037353516</v>
+        <v>80.07683563232422</v>
       </c>
       <c r="C230" t="n">
         <v>81.05000305175781</v>
@@ -6581,7 +6581,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>71.02316284179688</v>
+        <v>71.02317047119141</v>
       </c>
       <c r="C233" t="n">
         <v>71.66999816894531</v>
@@ -6697,7 +6697,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>99.49308013916016</v>
+        <v>99.49307250976562</v>
       </c>
       <c r="C237" t="n">
         <v>100.1500015258789</v>
